--- a/office/data/影响门店晚间收益调查数据.xlsx
+++ b/office/data/影响门店晚间收益调查数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cnplaman\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D16B0D02-3DC0-46C1-808D-37B7FAEE9EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E651096-B374-4C13-8713-1BE8BBA5D480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原始数据" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="153">
   <si>
     <t>未婚</t>
   </si>
@@ -1878,62 +1878,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C64:D66" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="平均值项:总消费金额" fld="15" subtotal="average" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C64:D66" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
@@ -2277,18 +2221,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" customWidth="1"/>
-    <col min="3" max="3" width="6.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="3" width="6.25" customWidth="1"/>
+    <col min="4" max="4" width="10.125" customWidth="1"/>
+    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2335,7 +2279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>97</v>
       </c>
@@ -2382,7 +2326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>98</v>
       </c>
@@ -2429,7 +2373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -2476,7 +2420,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,7 +2467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -2570,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -2617,7 +2561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -2664,7 +2608,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>99</v>
       </c>
@@ -2711,7 +2655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>100</v>
       </c>
@@ -2758,7 +2702,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>101</v>
       </c>
@@ -2805,7 +2749,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>102</v>
       </c>
@@ -2852,7 +2796,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -2899,7 +2843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>103</v>
       </c>
@@ -2946,7 +2890,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>104</v>
       </c>
@@ -2993,7 +2937,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>105</v>
       </c>
@@ -3040,7 +2984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>106</v>
       </c>
@@ -3087,7 +3031,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>47</v>
       </c>
@@ -3134,7 +3078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>107</v>
       </c>
@@ -3181,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
@@ -3228,7 +3172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>108</v>
       </c>
@@ -3275,7 +3219,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>109</v>
       </c>
@@ -3322,7 +3266,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>110</v>
       </c>
@@ -3369,7 +3313,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>111</v>
       </c>
@@ -3416,7 +3360,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>112</v>
       </c>
@@ -3463,7 +3407,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>113</v>
       </c>
@@ -3510,7 +3454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>114</v>
       </c>
@@ -3557,7 +3501,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>115</v>
       </c>
@@ -3604,7 +3548,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
@@ -3651,7 +3595,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>116</v>
       </c>
@@ -3698,7 +3642,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>117</v>
       </c>
@@ -3745,7 +3689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>118</v>
       </c>
@@ -3792,7 +3736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>119</v>
       </c>
@@ -3839,7 +3783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>120</v>
       </c>
@@ -3886,7 +3830,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>121</v>
       </c>
@@ -3933,7 +3877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>122</v>
       </c>
@@ -3980,7 +3924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>123</v>
       </c>
@@ -4027,7 +3971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>124</v>
       </c>
@@ -4074,7 +4018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>125</v>
       </c>
@@ -4121,7 +4065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>126</v>
       </c>
@@ -4168,7 +4112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>127</v>
       </c>
@@ -4215,7 +4159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>128</v>
       </c>
@@ -4262,7 +4206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>129</v>
       </c>
@@ -4309,7 +4253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>130</v>
       </c>
@@ -4356,7 +4300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>131</v>
       </c>
@@ -4403,7 +4347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>132</v>
       </c>
@@ -4450,7 +4394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>66</v>
       </c>
@@ -4497,7 +4441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>133</v>
       </c>
@@ -4544,7 +4488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>133</v>
       </c>
@@ -4591,7 +4535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -4638,7 +4582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>135</v>
       </c>
@@ -4685,7 +4629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>136</v>
       </c>
@@ -4732,7 +4676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>137</v>
       </c>
@@ -4779,7 +4723,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>138</v>
       </c>
@@ -4826,7 +4770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>139</v>
       </c>
@@ -4873,7 +4817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -4920,7 +4864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>141</v>
       </c>
@@ -4967,7 +4911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>142</v>
       </c>
@@ -5014,7 +4958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>143</v>
       </c>
@@ -5061,7 +5005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>74</v>
       </c>
@@ -5108,7 +5052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>144</v>
       </c>
@@ -5164,82 +5108,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q81"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q61"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="9.77734375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.75" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="9" width="9.21875" customWidth="1"/>
-    <col min="10" max="11" width="9.44140625" customWidth="1"/>
-    <col min="12" max="12" width="11.21875" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" customWidth="1"/>
-    <col min="15" max="15" width="9.21875" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="9" width="9.25" customWidth="1"/>
+    <col min="10" max="11" width="9.5" customWidth="1"/>
+    <col min="12" max="12" width="11.25" customWidth="1"/>
+    <col min="13" max="13" width="9.125" customWidth="1"/>
+    <col min="14" max="14" width="9.375" customWidth="1"/>
+    <col min="15" max="15" width="9.25" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" t="s">
         <v>17</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>97</v>
       </c>
       <c r="B2">
         <v>50</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" t="str">
         <f>IF(B2&lt;=20,"20岁以下",IF(B2&lt;40,"21-39岁","40岁以上"))</f>
         <v>40岁以上</v>
       </c>
@@ -5287,14 +5231,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>98</v>
       </c>
       <c r="B3">
         <v>50</v>
       </c>
-      <c r="C3" s="6" t="str">
+      <c r="C3" t="str">
         <f t="shared" ref="C3:C61" si="0">IF(B3&lt;=20,"20岁以下",IF(B3&lt;40,"21-39岁","40岁以上"))</f>
         <v>40岁以上</v>
       </c>
@@ -5342,14 +5286,14 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4">
         <v>27</v>
       </c>
-      <c r="C4" s="6" t="str">
+      <c r="C4" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -5397,14 +5341,14 @@
         <v>780</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="str">
+      <c r="C5" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -5452,14 +5396,14 @@
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>32</v>
       </c>
       <c r="B6">
         <v>24</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -5507,14 +5451,14 @@
         <v>560</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>33</v>
       </c>
       <c r="B7">
         <v>36</v>
       </c>
-      <c r="C7" s="6" t="str">
+      <c r="C7" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -5562,14 +5506,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>34</v>
       </c>
       <c r="B8">
         <v>29</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -5617,14 +5561,14 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>99</v>
       </c>
       <c r="B9">
         <v>53</v>
       </c>
-      <c r="C9" s="6" t="str">
+      <c r="C9" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -5672,21 +5616,21 @@
         <v>870</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>100</v>
       </c>
       <c r="B10">
         <v>32</v>
       </c>
-      <c r="C10" s="6" t="str">
+      <c r="C10" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>43</v>
       </c>
       <c r="F10">
@@ -5727,21 +5671,21 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>101</v>
       </c>
       <c r="B11">
         <v>45</v>
       </c>
-      <c r="C11" s="6" t="str">
+      <c r="C11" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>46</v>
       </c>
       <c r="F11">
@@ -5782,21 +5726,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>102</v>
       </c>
       <c r="B12">
         <v>20</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>48</v>
       </c>
       <c r="F12">
@@ -5837,21 +5781,21 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
         <v>41</v>
       </c>
       <c r="B13">
         <v>33</v>
       </c>
-      <c r="C13" s="6" t="str">
+      <c r="C13" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>46</v>
       </c>
       <c r="F13">
@@ -5892,21 +5836,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>103</v>
       </c>
       <c r="B14">
         <v>23</v>
       </c>
-      <c r="C14" s="6" t="str">
+      <c r="C14" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>36</v>
       </c>
       <c r="F14">
@@ -5947,21 +5891,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>104</v>
       </c>
       <c r="B15">
         <v>40</v>
       </c>
-      <c r="C15" s="6" t="str">
+      <c r="C15" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>56</v>
       </c>
       <c r="F15">
@@ -6002,14 +5946,14 @@
         <v>280</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>105</v>
       </c>
       <c r="B16">
         <v>42</v>
       </c>
-      <c r="C16" s="6" t="str">
+      <c r="C16" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -6057,14 +6001,14 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>106</v>
       </c>
       <c r="B17">
         <v>46</v>
       </c>
-      <c r="C17" s="6" t="str">
+      <c r="C17" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -6112,14 +6056,14 @@
         <v>380</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>47</v>
       </c>
       <c r="B18">
         <v>27</v>
       </c>
-      <c r="C18" s="6" t="str">
+      <c r="C18" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -6167,14 +6111,14 @@
         <v>630</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
         <v>107</v>
       </c>
       <c r="B19">
         <v>33</v>
       </c>
-      <c r="C19" s="6" t="str">
+      <c r="C19" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -6222,14 +6166,14 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
         <v>49</v>
       </c>
       <c r="B20">
         <v>18</v>
       </c>
-      <c r="C20" s="6" t="str">
+      <c r="C20" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
@@ -6277,14 +6221,14 @@
         <v>320</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
         <v>35</v>
       </c>
-      <c r="C21" s="6" t="str">
+      <c r="C21" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -6332,14 +6276,14 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
-      <c r="C22" s="6" t="str">
+      <c r="C22" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
@@ -6387,14 +6331,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
         <v>47</v>
       </c>
-      <c r="C23" s="6" t="str">
+      <c r="C23" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -6442,21 +6386,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
         <v>35</v>
       </c>
-      <c r="C24" s="6" t="str">
+      <c r="C24" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D24" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>76</v>
       </c>
       <c r="F24">
@@ -6497,21 +6441,21 @@
         <v>280</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
         <v>19</v>
       </c>
-      <c r="C25" s="6" t="str">
+      <c r="C25" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
       <c r="D25" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>79</v>
       </c>
       <c r="F25">
@@ -6552,21 +6496,21 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
         <v>20</v>
       </c>
-      <c r="C26" s="6" t="str">
+      <c r="C26" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
       <c r="D26" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>81</v>
       </c>
       <c r="F26">
@@ -6607,21 +6551,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
         <v>33</v>
       </c>
-      <c r="C27" s="6" t="str">
+      <c r="C27" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D27" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>43</v>
       </c>
       <c r="F27">
@@ -6662,21 +6606,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
         <v>23</v>
       </c>
-      <c r="C28" s="6" t="str">
+      <c r="C28" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D28" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>90</v>
       </c>
       <c r="F28">
@@ -6717,21 +6661,21 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
         <v>54</v>
       </c>
       <c r="B29">
         <v>57</v>
       </c>
-      <c r="C29" s="6" t="str">
+      <c r="C29" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D29" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29">
@@ -6772,21 +6716,21 @@
         <v>212</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
         <v>116</v>
       </c>
       <c r="B30">
         <v>37</v>
       </c>
-      <c r="C30" s="6" t="str">
+      <c r="C30" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D30" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>38</v>
       </c>
       <c r="F30">
@@ -6827,21 +6771,21 @@
         <v>280</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
         <v>117</v>
       </c>
       <c r="B31">
         <v>48</v>
       </c>
-      <c r="C31" s="6" t="str">
+      <c r="C31" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D31" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>46</v>
       </c>
       <c r="F31">
@@ -6882,14 +6826,14 @@
         <v>840</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
         <v>118</v>
       </c>
       <c r="B32">
         <v>54</v>
       </c>
-      <c r="C32" s="6" t="str">
+      <c r="C32" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -6937,14 +6881,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
         <v>119</v>
       </c>
       <c r="B33">
         <v>50</v>
       </c>
-      <c r="C33" s="6" t="str">
+      <c r="C33" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -6992,14 +6936,14 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
         <v>120</v>
       </c>
       <c r="B34">
         <v>27</v>
       </c>
-      <c r="C34" s="6" t="str">
+      <c r="C34" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7047,14 +6991,14 @@
         <v>780</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
         <v>121</v>
       </c>
       <c r="B35">
         <v>28</v>
       </c>
-      <c r="C35" s="6" t="str">
+      <c r="C35" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7102,14 +7046,14 @@
         <v>540</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
         <v>122</v>
       </c>
       <c r="B36">
         <v>24</v>
       </c>
-      <c r="C36" s="6" t="str">
+      <c r="C36" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7157,14 +7101,14 @@
         <v>560</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
         <v>123</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-      <c r="C37" s="6" t="str">
+      <c r="C37" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7212,14 +7156,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
         <v>124</v>
       </c>
       <c r="B38">
         <v>29</v>
       </c>
-      <c r="C38" s="6" t="str">
+      <c r="C38" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7267,14 +7211,14 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
         <v>125</v>
       </c>
       <c r="B39">
         <v>53</v>
       </c>
-      <c r="C39" s="6" t="str">
+      <c r="C39" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -7322,21 +7266,21 @@
         <v>870</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A40" t="s">
         <v>126</v>
       </c>
       <c r="B40">
         <v>32</v>
       </c>
-      <c r="C40" s="6" t="str">
+      <c r="C40" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>36</v>
       </c>
       <c r="F40">
@@ -7377,21 +7321,21 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
         <v>127</v>
       </c>
       <c r="B41">
         <v>48</v>
       </c>
-      <c r="C41" s="6" t="str">
+      <c r="C41" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" t="s">
         <v>25</v>
       </c>
       <c r="F41">
@@ -7432,21 +7376,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
         <v>128</v>
       </c>
       <c r="B42">
         <v>20</v>
       </c>
-      <c r="C42" s="6" t="str">
+      <c r="C42" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>36</v>
       </c>
       <c r="F42">
@@ -7487,21 +7431,21 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
         <v>129</v>
       </c>
       <c r="B43">
         <v>33</v>
       </c>
-      <c r="C43" s="6" t="str">
+      <c r="C43" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" t="s">
         <v>25</v>
       </c>
       <c r="F43">
@@ -7542,21 +7486,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
         <v>130</v>
       </c>
       <c r="B44">
         <v>23</v>
       </c>
-      <c r="C44" s="6" t="str">
+      <c r="C44" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" t="s">
         <v>36</v>
       </c>
       <c r="F44">
@@ -7597,21 +7541,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A45" t="s">
         <v>131</v>
       </c>
       <c r="B45">
         <v>40</v>
       </c>
-      <c r="C45" s="6" t="str">
+      <c r="C45" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D45" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" t="s">
         <v>36</v>
       </c>
       <c r="F45">
@@ -7652,14 +7596,14 @@
         <v>280</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A46" t="s">
         <v>132</v>
       </c>
       <c r="B46">
         <v>42</v>
       </c>
-      <c r="C46" s="6" t="str">
+      <c r="C46" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -7707,14 +7651,14 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A47" t="s">
         <v>66</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-      <c r="C47" s="6" t="str">
+      <c r="C47" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -7762,14 +7706,14 @@
         <v>760</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A48" t="s">
         <v>133</v>
       </c>
       <c r="B48">
         <v>27</v>
       </c>
-      <c r="C48" s="6" t="str">
+      <c r="C48" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7817,14 +7761,14 @@
         <v>420</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A49" t="s">
         <v>133</v>
       </c>
       <c r="B49">
         <v>33</v>
       </c>
-      <c r="C49" s="6" t="str">
+      <c r="C49" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7872,14 +7816,14 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A50" t="s">
         <v>134</v>
       </c>
       <c r="B50">
         <v>18</v>
       </c>
-      <c r="C50" s="6" t="str">
+      <c r="C50" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
@@ -7927,14 +7871,14 @@
         <v>320</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A51" t="s">
         <v>135</v>
       </c>
       <c r="B51">
         <v>35</v>
       </c>
-      <c r="C51" s="6" t="str">
+      <c r="C51" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
@@ -7982,14 +7926,14 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A52" t="s">
         <v>136</v>
       </c>
       <c r="B52">
         <v>17</v>
       </c>
-      <c r="C52" s="6" t="str">
+      <c r="C52" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
@@ -8037,14 +7981,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A53" t="s">
         <v>137</v>
       </c>
       <c r="B53">
         <v>50</v>
       </c>
-      <c r="C53" s="6" t="str">
+      <c r="C53" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
@@ -8092,21 +8036,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A54" t="s">
         <v>138</v>
       </c>
       <c r="B54">
         <v>35</v>
       </c>
-      <c r="C54" s="6" t="str">
+      <c r="C54" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D54" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54">
@@ -8147,21 +8091,21 @@
         <v>280</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A55" t="s">
         <v>139</v>
       </c>
       <c r="B55">
         <v>19</v>
       </c>
-      <c r="C55" s="6" t="str">
+      <c r="C55" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" t="s">
         <v>36</v>
       </c>
       <c r="F55">
@@ -8202,21 +8146,21 @@
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A56" t="s">
         <v>140</v>
       </c>
       <c r="B56">
         <v>20</v>
       </c>
-      <c r="C56" s="6" t="str">
+      <c r="C56" t="str">
         <f t="shared" si="0"/>
         <v>20岁以下</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>36</v>
       </c>
       <c r="F56">
@@ -8257,21 +8201,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A57" t="s">
         <v>141</v>
       </c>
       <c r="B57">
         <v>33</v>
       </c>
-      <c r="C57" s="6" t="str">
+      <c r="C57" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D57" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>36</v>
       </c>
       <c r="F57">
@@ -8312,21 +8256,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A58" t="s">
         <v>142</v>
       </c>
       <c r="B58">
         <v>23</v>
       </c>
-      <c r="C58" s="6" t="str">
+      <c r="C58" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" t="s">
         <v>36</v>
       </c>
       <c r="F58">
@@ -8367,21 +8311,21 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A59" t="s">
         <v>143</v>
       </c>
       <c r="B59">
         <v>50</v>
       </c>
-      <c r="C59" s="6" t="str">
+      <c r="C59" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59">
@@ -8422,21 +8366,21 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A60" t="s">
         <v>74</v>
       </c>
       <c r="B60">
         <v>37</v>
       </c>
-      <c r="C60" s="6" t="str">
+      <c r="C60" t="str">
         <f t="shared" si="0"/>
         <v>21-39岁</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60">
@@ -8477,21 +8421,21 @@
         <v>560</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A61" t="s">
         <v>144</v>
       </c>
       <c r="B61">
         <v>48</v>
       </c>
-      <c r="C61" s="6" t="str">
+      <c r="C61" t="str">
         <f t="shared" si="0"/>
         <v>40岁以上</v>
       </c>
       <c r="D61" t="s">
         <v>23</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" t="s">
         <v>25</v>
       </c>
       <c r="F61">
@@ -8532,98 +8476,23 @@
         <v>840</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C64" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D64" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D65">
-        <v>502.66666666666669</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D66">
-        <v>175.26666666666668</v>
-      </c>
-    </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C67" t="s">
-        <v>151</v>
-      </c>
-      <c r="D67">
-        <f>GETPIVOTDATA("总消费金额",$C$64,"性别","男")-GETPIVOTDATA("总消费金额",$C$64,"性别","女")</f>
-        <v>327.39999999999998</v>
-      </c>
-    </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C68"/>
-    </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C69"/>
-    </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C70"/>
-    </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71"/>
-    </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72"/>
-    </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73"/>
-    </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C74"/>
-    </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75"/>
-    </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C76"/>
-    </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C77"/>
-    </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78"/>
-    </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C79"/>
-    </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C80"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11.77734375" customWidth="1"/>
+    <col min="17" max="17" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -8676,7 +8545,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>98</v>
       </c>
@@ -8731,7 +8600,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -8786,7 +8655,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -8841,7 +8710,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -8896,7 +8765,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>99</v>
       </c>
@@ -8951,7 +8820,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>100</v>
       </c>
@@ -9006,7 +8875,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>103</v>
       </c>
@@ -9061,7 +8930,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>104</v>
       </c>
@@ -9116,7 +8985,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>106</v>
       </c>
@@ -9171,7 +9040,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
@@ -9226,7 +9095,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>111</v>
       </c>
@@ -9281,7 +9150,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>114</v>
       </c>
@@ -9336,7 +9205,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>115</v>
       </c>
@@ -9391,7 +9260,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>116</v>
       </c>
@@ -9446,7 +9315,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>117</v>
       </c>
@@ -9501,7 +9370,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>119</v>
       </c>
@@ -9556,7 +9425,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>120</v>
       </c>
@@ -9611,7 +9480,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>121</v>
       </c>
@@ -9666,7 +9535,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>122</v>
       </c>
@@ -9721,7 +9590,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>125</v>
       </c>
@@ -9776,7 +9645,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>126</v>
       </c>
@@ -9831,7 +9700,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>130</v>
       </c>
@@ -9886,7 +9755,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>131</v>
       </c>
@@ -9941,7 +9810,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -9996,7 +9865,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>134</v>
       </c>
@@ -10051,7 +9920,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>138</v>
       </c>
@@ -10106,7 +9975,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>141</v>
       </c>
@@ -10161,7 +10030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>142</v>
       </c>
@@ -10216,7 +10085,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -10271,7 +10140,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>144</v>
       </c>
@@ -10326,7 +10195,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
@@ -10381,7 +10250,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
@@ -10436,7 +10305,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -10491,7 +10360,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
@@ -10546,7 +10415,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>102</v>
       </c>
@@ -10601,7 +10470,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
@@ -10656,7 +10525,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>105</v>
       </c>
@@ -10711,7 +10580,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -10766,7 +10635,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>107</v>
       </c>
@@ -10821,7 +10690,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>108</v>
       </c>
@@ -10876,7 +10745,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>109</v>
       </c>
@@ -10931,7 +10800,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>110</v>
       </c>
@@ -10986,7 +10855,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>112</v>
       </c>
@@ -11041,7 +10910,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>113</v>
       </c>
@@ -11096,7 +10965,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -11151,7 +11020,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>118</v>
       </c>
@@ -11206,7 +11075,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
@@ -11261,7 +11130,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>124</v>
       </c>
@@ -11316,7 +11185,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>127</v>
       </c>
@@ -11371,7 +11240,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>128</v>
       </c>
@@ -11426,7 +11295,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>129</v>
       </c>
@@ -11481,7 +11350,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>132</v>
       </c>
@@ -11536,7 +11405,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>133</v>
       </c>
@@ -11591,7 +11460,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>133</v>
       </c>
@@ -11646,7 +11515,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>135</v>
       </c>
@@ -11701,7 +11570,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>136</v>
       </c>
@@ -11756,7 +11625,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>137</v>
       </c>
@@ -11811,7 +11680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>139</v>
       </c>
@@ -11866,7 +11735,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>140</v>
       </c>
@@ -11921,7 +11790,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>143</v>
       </c>
@@ -11976,13 +11845,13 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C64" s="7" t="s">
         <v>147</v>
       </c>
@@ -11997,7 +11866,7 @@
         <v>2.0496336668530502E-5</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.15">
       <c r="C65" s="2" t="s">
         <v>148</v>
       </c>
@@ -12005,7 +11874,7 @@
         <v>502.66666666666669</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.15">
       <c r="C66" s="2" t="s">
         <v>149</v>
       </c>
@@ -12013,7 +11882,7 @@
         <v>175.26666666666668</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.15">
       <c r="C67" t="s">
         <v>151</v>
       </c>
